--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775F68BF-6B92-4842-B082-072A1CBCCDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="3600" windowWidth="26505" windowHeight="14550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="3276" windowWidth="26508" windowHeight="14556"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$Q$25</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -974,7 +970,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1262,23 +1258,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1004"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1328,7 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1379,14 +1375,14 @@
         <v>350000</v>
       </c>
       <c r="P2" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q2" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -1433,14 +1429,14 @@
         <v>290000</v>
       </c>
       <c r="P3" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q3" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -1487,14 +1483,14 @@
         <v>350000</v>
       </c>
       <c r="P4" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q4" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1523,7 +1519,7 @@
         <v>460000</v>
       </c>
       <c r="J5" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K5" s="2">
         <v>300000</v>
@@ -1535,20 +1531,20 @@
         <v>30000</v>
       </c>
       <c r="N5" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O5" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P5" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q5" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1573,7 @@
         <v>360000</v>
       </c>
       <c r="J6" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K6" s="2">
         <v>300000</v>
@@ -1589,20 +1585,20 @@
         <v>30000</v>
       </c>
       <c r="N6" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O6" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P6" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q6" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1631,7 +1627,7 @@
         <v>360000</v>
       </c>
       <c r="J7" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K7" s="2">
         <v>300000</v>
@@ -1643,20 +1639,20 @@
         <v>30000</v>
       </c>
       <c r="N7" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O7" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P7" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q7" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1685,7 +1681,7 @@
         <v>460000</v>
       </c>
       <c r="J8" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K8" s="2">
         <v>300000</v>
@@ -1697,20 +1693,20 @@
         <v>30000</v>
       </c>
       <c r="N8" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O8" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P8" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q8" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1739,7 +1735,7 @@
         <v>360000</v>
       </c>
       <c r="J9" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K9" s="2">
         <v>300000</v>
@@ -1751,20 +1747,20 @@
         <v>30000</v>
       </c>
       <c r="N9" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O9" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P9" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q9" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -1793,7 +1789,7 @@
         <v>360000</v>
       </c>
       <c r="J10" s="2">
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="K10" s="2">
         <v>300000</v>
@@ -1805,20 +1801,20 @@
         <v>30000</v>
       </c>
       <c r="N10" s="2">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="O10" s="2">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="P10" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q10" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1847,7 +1843,7 @@
         <v>500000</v>
       </c>
       <c r="J11" s="2">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="K11" s="2">
         <v>200000</v>
@@ -1859,20 +1855,20 @@
         <v>30000</v>
       </c>
       <c r="N11" s="2">
-        <v>350000</v>
+        <v>500000</v>
       </c>
       <c r="O11" s="2">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="P11" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q11" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1901,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="K12" s="2">
         <v>200000</v>
@@ -1913,20 +1909,20 @@
         <v>30000</v>
       </c>
       <c r="N12" s="2">
-        <v>350000</v>
+        <v>500000</v>
       </c>
       <c r="O12" s="2">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="P12" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q12" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1955,10 +1951,10 @@
         <v>500000</v>
       </c>
       <c r="J13" s="2">
-        <v>300000</v>
+        <v>654900</v>
       </c>
       <c r="K13" s="2">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="L13" s="2">
         <v>30000</v>
@@ -1967,20 +1963,20 @@
         <v>30000</v>
       </c>
       <c r="N13" s="2">
-        <v>350000</v>
+        <v>654900</v>
       </c>
       <c r="O13" s="2">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="P13" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q13" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -2027,14 +2023,14 @@
         <v>250000</v>
       </c>
       <c r="P14" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q14" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2081,14 +2077,14 @@
         <v>0</v>
       </c>
       <c r="P15" s="2">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Q15" s="2">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -2117,7 +2113,7 @@
         <v>445900</v>
       </c>
       <c r="J16" s="2">
-        <v>150000</v>
+        <v>445900</v>
       </c>
       <c r="K16" s="2">
         <v>30000</v>
@@ -2129,20 +2125,20 @@
         <v>30000</v>
       </c>
       <c r="N16" s="2">
-        <v>200000</v>
+        <v>445900</v>
       </c>
       <c r="O16" s="2">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="P16" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q16" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -2171,10 +2167,10 @@
         <v>400000</v>
       </c>
       <c r="J17" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="K17" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="L17" s="2">
         <v>30000</v>
@@ -2183,20 +2179,20 @@
         <v>30000</v>
       </c>
       <c r="N17" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="O17" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="P17" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q17" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -2225,10 +2221,10 @@
         <v>340000</v>
       </c>
       <c r="J18" s="2">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K18" s="2">
-        <v>290000</v>
+        <v>450000</v>
       </c>
       <c r="L18" s="2">
         <v>30000</v>
@@ -2237,20 +2233,20 @@
         <v>30000</v>
       </c>
       <c r="N18" s="2">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="O18" s="2">
-        <v>290000</v>
+        <v>450000</v>
       </c>
       <c r="P18" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q18" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -2297,14 +2293,14 @@
         <v>490000</v>
       </c>
       <c r="P19" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q19" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2333,10 +2329,10 @@
         <v>400000</v>
       </c>
       <c r="J20" s="2">
-        <v>410000</v>
+        <v>400000</v>
       </c>
       <c r="K20" s="2">
-        <v>410000</v>
+        <v>400000</v>
       </c>
       <c r="L20" s="2">
         <v>30000</v>
@@ -2345,20 +2341,20 @@
         <v>30000</v>
       </c>
       <c r="N20" s="2">
-        <v>410000</v>
+        <v>400000</v>
       </c>
       <c r="O20" s="2">
-        <v>410000</v>
+        <v>400000</v>
       </c>
       <c r="P20" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q20" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -2387,10 +2383,10 @@
         <v>340000</v>
       </c>
       <c r="J21" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="K21" s="2">
-        <v>290000</v>
+        <v>400000</v>
       </c>
       <c r="L21" s="2">
         <v>30000</v>
@@ -2399,20 +2395,20 @@
         <v>30000</v>
       </c>
       <c r="N21" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="O21" s="2">
-        <v>290000</v>
+        <v>400000</v>
       </c>
       <c r="P21" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q21" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -2459,14 +2455,14 @@
         <v>490000</v>
       </c>
       <c r="P22" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="Q22" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -2513,14 +2509,14 @@
         <v>30000</v>
       </c>
       <c r="P23" s="2">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="Q23" s="2">
         <v>30000</v>
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2567,14 +2563,14 @@
         <v>30000</v>
       </c>
       <c r="P24" s="2">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="Q24" s="2">
         <v>30000</v>
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -2628,7 +2624,7 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2648,7 +2644,7 @@
       <c r="Q26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2668,7 +2664,7 @@
       <c r="Q27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2688,7 +2684,7 @@
       <c r="Q28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2708,7 +2704,7 @@
       <c r="Q29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2728,7 +2724,7 @@
       <c r="Q30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2748,7 +2744,7 @@
       <c r="Q31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2768,978 +2764,978 @@
       <c r="Q32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3747,18 +3743,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4D3BD6-20BD-4BC1-8ACF-89E71C52B66B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3839,7 +3835,7 @@
       </c>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -3920,7 +3916,7 @@
       </c>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -4001,7 +3997,7 @@
       </c>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -4082,7 +4078,7 @@
       </c>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -4163,7 +4159,7 @@
       </c>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -4244,7 +4240,7 @@
       </c>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -4325,7 +4321,7 @@
       </c>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -4406,7 +4402,7 @@
       </c>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -4487,7 +4483,7 @@
       </c>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -4568,7 +4564,7 @@
       </c>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -4649,7 +4645,7 @@
       </c>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -4730,7 +4726,7 @@
       </c>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -4811,7 +4807,7 @@
       </c>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -4892,7 +4888,7 @@
       </c>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -4923,7 +4919,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -5004,7 +5000,7 @@
       </c>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -5085,7 +5081,7 @@
       </c>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -5166,7 +5162,7 @@
       </c>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -5247,7 +5243,7 @@
       </c>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -5328,7 +5324,7 @@
       </c>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -5409,7 +5405,7 @@
       </c>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -5490,7 +5486,7 @@
       </c>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -5571,7 +5567,7 @@
       </c>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -5652,7 +5648,7 @@
       </c>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -5733,985 +5729,985 @@
       </c>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6720,18 +6716,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6814,7 +6810,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -6897,7 +6893,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -6980,7 +6976,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -7063,7 +7059,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -7146,7 +7142,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -7229,7 +7225,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -7312,7 +7308,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -7395,7 +7391,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -7478,7 +7474,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -7561,7 +7557,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -7644,7 +7640,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -7727,7 +7723,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -7810,7 +7806,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -7893,7 +7889,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -7976,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -8059,7 +8055,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -8142,7 +8138,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -8225,7 +8221,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -8308,7 +8304,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -8391,7 +8387,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -8474,7 +8470,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -8557,7 +8553,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -8568,7 +8564,7 @@
         <v>42000</v>
       </c>
       <c r="D23" s="3">
-        <v>52000</v>
+        <v>49000</v>
       </c>
       <c r="E23" s="3">
         <v>60000</v>
@@ -8592,7 +8588,7 @@
         <v>86000</v>
       </c>
       <c r="L23" s="3">
-        <v>88000</v>
+        <v>89000</v>
       </c>
       <c r="M23" s="3">
         <v>91000</v>
@@ -8640,7 +8636,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -8651,7 +8647,7 @@
         <v>42000</v>
       </c>
       <c r="D24" s="3">
-        <v>52000</v>
+        <v>49000</v>
       </c>
       <c r="E24" s="3">
         <v>60000</v>
@@ -8723,7 +8719,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -8806,985 +8802,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9793,18 +9789,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9887,7 +9883,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -9970,7 +9966,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -10053,7 +10049,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -10136,7 +10132,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -10219,7 +10215,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -10302,7 +10298,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -10385,7 +10381,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -10468,7 +10464,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -10551,7 +10547,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -10634,7 +10630,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -10717,7 +10713,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -10800,7 +10796,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -10883,7 +10879,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -10966,7 +10962,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -11049,7 +11045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -11132,7 +11128,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -11215,7 +11211,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -11298,7 +11294,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -11381,7 +11377,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -11464,7 +11460,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -11547,7 +11543,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -11630,7 +11626,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -11713,7 +11709,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -11796,7 +11792,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -11879,985 +11875,985 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_01FE2CA4244CFB60C5076EB417057EA2E8507461" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="3276" windowWidth="26508" windowHeight="14556"/>
+    <workbookView xWindow="6540" yWindow="3276" windowWidth="26508" windowHeight="14556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$Q$25</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -970,7 +971,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1258,23 +1259,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1004"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.40625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.76171875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="12.5390625" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="16.31640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1382,7 +1383,7 @@
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -1436,7 +1437,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -1490,7 +1491,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1507,16 +1508,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G5" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H5" s="2">
-        <v>460000</v>
+        <v>400000</v>
       </c>
       <c r="I5" s="2">
-        <v>460000</v>
+        <v>400000</v>
       </c>
       <c r="J5" s="2">
         <v>360000</v>
@@ -1544,7 +1545,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1561,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G6" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="H6" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I6" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="J6" s="2">
         <v>360000</v>
@@ -1598,7 +1599,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1615,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G7" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="H7" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I7" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="J7" s="2">
         <v>360000</v>
@@ -1652,7 +1653,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1669,16 +1670,16 @@
         <v>350000</v>
       </c>
       <c r="F8" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G8" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H8" s="2">
-        <v>460000</v>
+        <v>400000</v>
       </c>
       <c r="I8" s="2">
-        <v>460000</v>
+        <v>400000</v>
       </c>
       <c r="J8" s="2">
         <v>360000</v>
@@ -1706,7 +1707,7 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1723,16 +1724,16 @@
         <v>400000</v>
       </c>
       <c r="F9" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G9" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I9" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="J9" s="2">
         <v>360000</v>
@@ -1760,7 +1761,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -1777,16 +1778,16 @@
         <v>350000</v>
       </c>
       <c r="F10" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G10" s="2">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="H10" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I10" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="J10" s="2">
         <v>360000</v>
@@ -1814,7 +1815,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1868,7 +1869,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1999,10 +2000,10 @@
         <v>520000</v>
       </c>
       <c r="H14" s="2">
-        <v>540000</v>
+        <v>500000</v>
       </c>
       <c r="I14" s="2">
-        <v>520000</v>
+        <v>500000</v>
       </c>
       <c r="J14" s="2">
         <v>300000</v>
@@ -2030,7 +2031,7 @@
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2084,7 +2085,7 @@
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -2138,7 +2139,7 @@
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -2155,16 +2156,16 @@
         <v>450000</v>
       </c>
       <c r="F17" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G17" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H17" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I17" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="J17" s="2">
         <v>450000</v>
@@ -2192,7 +2193,7 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -2209,16 +2210,16 @@
         <v>340000</v>
       </c>
       <c r="F18" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G18" s="2">
-        <v>290000</v>
+        <v>400000</v>
       </c>
       <c r="H18" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I18" s="2">
-        <v>340000</v>
+        <v>500000</v>
       </c>
       <c r="J18" s="2">
         <v>450000</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -2263,16 +2264,16 @@
         <v>500000</v>
       </c>
       <c r="F19" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G19" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H19" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I19" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="J19" s="2">
         <v>490000</v>
@@ -2300,7 +2301,7 @@
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2317,16 +2318,16 @@
         <v>450000</v>
       </c>
       <c r="F20" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G20" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H20" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I20" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="J20" s="2">
         <v>400000</v>
@@ -2354,7 +2355,7 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -2371,16 +2372,16 @@
         <v>340000</v>
       </c>
       <c r="F21" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G21" s="2">
-        <v>290000</v>
+        <v>400000</v>
       </c>
       <c r="H21" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I21" s="2">
-        <v>340000</v>
+        <v>500000</v>
       </c>
       <c r="J21" s="2">
         <v>400000</v>
@@ -2408,7 +2409,7 @@
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -2425,16 +2426,16 @@
         <v>500000</v>
       </c>
       <c r="F22" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G22" s="2">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H22" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="I22" s="2">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="J22" s="2">
         <v>490000</v>
@@ -2462,7 +2463,7 @@
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -2516,7 +2517,7 @@
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2570,7 +2571,7 @@
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -2624,7 +2625,7 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2644,7 +2645,7 @@
       <c r="Q26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2664,7 +2665,7 @@
       <c r="Q27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2684,7 +2685,7 @@
       <c r="Q28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2704,7 +2705,7 @@
       <c r="Q29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2724,7 +2725,7 @@
       <c r="Q30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2744,7 +2745,7 @@
       <c r="Q31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2764,978 +2765,978 @@
       <c r="Q32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3743,18 +3744,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3835,7 +3836,7 @@
       </c>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -3916,7 +3917,7 @@
       </c>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -3997,7 +3998,7 @@
       </c>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -4078,7 +4079,7 @@
       </c>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -4159,7 +4160,7 @@
       </c>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -4240,7 +4241,7 @@
       </c>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -4321,7 +4322,7 @@
       </c>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -4402,7 +4403,7 @@
       </c>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -4483,7 +4484,7 @@
       </c>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -4564,7 +4565,7 @@
       </c>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -4645,7 +4646,7 @@
       </c>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -4726,7 +4727,7 @@
       </c>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -4807,7 +4808,7 @@
       </c>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -4888,7 +4889,7 @@
       </c>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -4919,7 +4920,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -5000,7 +5001,7 @@
       </c>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -5081,7 +5082,7 @@
       </c>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -5162,7 +5163,7 @@
       </c>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -5243,7 +5244,7 @@
       </c>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -5324,7 +5325,7 @@
       </c>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -5405,7 +5406,7 @@
       </c>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -5567,7 +5568,7 @@
       </c>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -5648,7 +5649,7 @@
       </c>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -5729,985 +5730,985 @@
       </c>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6716,18 +6717,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6810,7 +6811,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -6893,7 +6894,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -6976,7 +6977,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -7059,7 +7060,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -7142,7 +7143,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -7225,7 +7226,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -7308,7 +7309,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -7391,7 +7392,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -7474,7 +7475,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -7640,7 +7641,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -7723,7 +7724,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -7806,7 +7807,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -7972,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -8055,7 +8056,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -8138,7 +8139,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -8221,7 +8222,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -8304,7 +8305,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -8387,7 +8388,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -8470,7 +8471,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -8553,7 +8554,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -8719,7 +8720,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -8802,985 +8803,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9789,18 +9790,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9883,7 +9884,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -9966,7 +9967,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -10049,7 +10050,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -10132,7 +10133,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -10215,7 +10216,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -10381,7 +10382,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -10464,7 +10465,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -10547,7 +10548,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -10630,7 +10631,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -10713,7 +10714,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -10879,7 +10880,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -10962,7 +10963,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -11045,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -11128,7 +11129,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -11211,7 +11212,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -11377,7 +11378,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -11460,7 +11461,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -11543,7 +11544,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -11626,7 +11627,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -11709,7 +11710,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -11792,7 +11793,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -11875,985 +11876,985 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="43">
   <si>
     <t>모델명</t>
   </si>
@@ -967,6 +967,12 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>워치9 44mm</t>
+  </si>
+  <si>
+    <t>워치9 40mm</t>
+  </si>
 </sst>
 </file>
 
@@ -1033,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1043,6 +1049,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2626,43 +2638,57 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
+        <v>379000</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2">
+        <v>325800</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2">
+        <v>379000</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2">
+        <v>365000</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5730,8 +5756,91 @@
       </c>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="D27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="F27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="G27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="I27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="J27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="K27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="L27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="M27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="N27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="O27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="P27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="R27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="S27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="T27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="U27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="V27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="W27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="X27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>100000</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>100000</v>
+      </c>
+    </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -8803,8 +8912,172 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="C26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="D26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="E26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="F26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="G26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="H26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="I26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="J26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="K26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="L26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="M26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="N26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="O26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="P26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="R26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="S26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="T26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="U26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="V26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="W26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="X26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>379000</v>
+      </c>
+      <c r="AA26" s="6">
+        <v>379000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="D27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="F27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="G27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="H27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="I27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="J27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="K27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="L27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="M27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="N27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="O27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="P27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="R27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="S27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="T27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="U27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="V27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="W27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="X27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>379000</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>379000</v>
+      </c>
+    </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11876,8 +12149,172 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="C26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="D26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="E26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="F26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="G26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="H26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="I26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="J26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="K26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="L26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="M26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="N26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="O26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="P26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="R26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="S26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="T26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="U26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="V26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="W26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="X26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>325800</v>
+      </c>
+      <c r="AA26" s="6">
+        <v>325800</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="D27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="F27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="G27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="H27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="I27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="J27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="K27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="L27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="M27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="N27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="O27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="P27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="R27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="S27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="T27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="U27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="V27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="W27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="X27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>365000</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>365000</v>
+      </c>
+    </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -5766,79 +5766,79 @@
         <v>42</v>
       </c>
       <c r="B27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="C27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="E27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="H27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="J27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="K27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="L27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="M27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="N27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="O27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="P27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="Q27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="R27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="S27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="T27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="U27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="V27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="W27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="X27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="Y27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="Z27" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -8917,82 +8917,82 @@
         <v>41</v>
       </c>
       <c r="B26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="C26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="D26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="E26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="F26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="G26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="H26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="I26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="J26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="K26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="L26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="M26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="N26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="O26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="P26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Q26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="R26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="S26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="T26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="U26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="V26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="W26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="X26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Y26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Z26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="AA26" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -9000,82 +9000,82 @@
         <v>42</v>
       </c>
       <c r="B27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="C27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="D27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="E27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="F27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="G27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="H27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="I27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="J27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="K27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="L27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="M27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="N27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="O27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="P27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Q27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="R27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="S27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="T27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="U27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="V27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="W27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="X27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Y27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="Z27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
       <c r="AA27" s="6">
-        <v>379000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -12154,82 +12154,82 @@
         <v>41</v>
       </c>
       <c r="B26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="C26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="D26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="E26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="F26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="G26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="H26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="I26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="J26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="K26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="L26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="M26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="N26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="O26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="P26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="Q26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="R26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="S26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="T26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="U26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="V26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="W26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="X26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="Y26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="Z26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
       <c r="AA26" s="6">
-        <v>325800</v>
+        <v>164000</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -12237,82 +12237,82 @@
         <v>42</v>
       </c>
       <c r="B27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="C27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="D27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="E27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="F27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="G27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="H27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="I27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="J27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="K27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="L27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="M27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="N27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="O27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="P27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="Q27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="R27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="S27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="T27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="U27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="V27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="W27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="X27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="Y27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="Z27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
       <c r="AA27" s="6">
-        <v>365000</v>
+        <v>164000</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -2213,13 +2213,13 @@
         <v>350000</v>
       </c>
       <c r="C18" s="4">
-        <v>290000</v>
+        <v>330000</v>
       </c>
       <c r="D18" s="4">
         <v>400000</v>
       </c>
       <c r="E18" s="4">
-        <v>340000</v>
+        <v>380000</v>
       </c>
       <c r="F18" s="2">
         <v>400000</v>

--- a/policy_20260901.xlsx
+++ b/policy_20260901.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_01FE2CA4244CFB60C5076EB417057EA2E8507461" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CE371C-EC60-4966-9142-D278BB1E4416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="3276" windowWidth="26508" windowHeight="14556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="3945" windowWidth="26505" windowHeight="14550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -25,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1276,18 +1279,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1004"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.40625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.76171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="12.5390625" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="16.31640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1344,7 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1395,7 +1398,7 @@
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -1449,7 +1452,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -1503,7 +1506,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1557,7 +1560,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1611,7 +1614,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1665,7 +1668,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1719,7 +1722,7 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +1776,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -1827,7 +1830,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1881,7 +1884,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1935,7 +1938,7 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1989,7 +1992,7 @@
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -2043,7 +2046,7 @@
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2097,7 +2100,7 @@
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -2151,7 +2154,7 @@
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -2205,7 +2208,7 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -2259,7 +2262,7 @@
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -2313,7 +2316,7 @@
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2367,7 +2370,7 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -2421,7 +2424,7 @@
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -2475,7 +2478,7 @@
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -2529,7 +2532,7 @@
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2583,7 +2586,7 @@
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -2637,7 +2640,7 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
@@ -2663,7 +2666,7 @@
       <c r="Q26" s="2"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -2691,7 +2694,7 @@
       <c r="Q27" s="2"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2711,7 +2714,7 @@
       <c r="Q28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2731,7 +2734,7 @@
       <c r="Q29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2751,7 +2754,7 @@
       <c r="Q30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2771,7 +2774,7 @@
       <c r="Q31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2791,978 +2794,978 @@
       <c r="Q32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3775,13 +3778,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3862,7 +3865,7 @@
       </c>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -3943,7 +3946,7 @@
       </c>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -4024,7 +4027,7 @@
       </c>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -4105,7 +4108,7 @@
       </c>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -4186,7 +4189,7 @@
       </c>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -4267,7 +4270,7 @@
       </c>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -4348,7 +4351,7 @@
       </c>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -4429,7 +4432,7 @@
       </c>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -4510,7 +4513,7 @@
       </c>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -4591,7 +4594,7 @@
       </c>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -4672,7 +4675,7 @@
       </c>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -4753,7 +4756,7 @@
       </c>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -4834,7 +4837,7 @@
       </c>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -4915,38 +4918,88 @@
       </c>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="B15" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D15" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K15" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L15" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M15" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N15" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O15" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P15" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R15" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S15" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T15" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U15" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W15" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X15" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -5027,7 +5080,7 @@
       </c>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -5108,7 +5161,7 @@
       </c>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -5189,7 +5242,7 @@
       </c>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -5270,7 +5323,7 @@
       </c>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -5351,7 +5404,7 @@
       </c>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -5432,7 +5485,7 @@
       </c>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -5513,7 +5566,7 @@
       </c>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -5594,7 +5647,7 @@
       </c>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -5675,7 +5728,7 @@
       </c>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -5756,12 +5809,12 @@
       </c>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -5841,983 +5894,983 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6831,13 +6884,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6920,7 +6973,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -7003,7 +7056,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -7086,7 +7139,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -7169,7 +7222,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -7252,7 +7305,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -7335,7 +7388,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -7418,7 +7471,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -7501,7 +7554,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -7584,7 +7637,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -7667,7 +7720,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -7750,7 +7803,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -7833,7 +7886,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -7916,7 +7969,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -7999,7 +8052,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -8082,7 +8135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -8165,7 +8218,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -8248,7 +8301,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -8331,7 +8384,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -8414,7 +8467,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -8497,7 +8550,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -8580,7 +8633,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -8663,7 +8716,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -8746,7 +8799,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -8829,7 +8882,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -8912,7 +8965,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
@@ -8995,7 +9048,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -9078,983 +9131,983 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10068,13 +10121,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1004"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10157,7 +10210,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -10240,7 +10293,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -10323,7 +10376,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -10406,7 +10459,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -10489,7 +10542,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -10572,7 +10625,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -10655,7 +10708,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -10738,7 +10791,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -10821,7 +10874,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -10904,7 +10957,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -10987,7 +11040,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -11070,7 +11123,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -11153,7 +11206,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -11236,7 +11289,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -11247,79 +11300,79 @@
         <v>0</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>222000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>233000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>257000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>262000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>268000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>291000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>326000</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>361000</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>373000</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>390000</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>402000</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>414000</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>442000</v>
       </c>
       <c r="V15" s="3">
-        <v>0</v>
+        <v>460000</v>
       </c>
       <c r="W15" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="X15" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Y15" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Z15" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -11402,7 +11455,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -11485,7 +11538,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -11568,7 +11621,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -11651,7 +11704,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -11734,7 +11787,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -11817,7 +11870,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -11900,7 +11953,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -11983,7 +12036,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -12066,7 +12119,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -12149,7 +12202,7 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
@@ -12232,7 +12285,7 @@
         <v>164000</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -12315,983 +12368,983 @@
         <v>164000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
